--- a/Submission/Table 4.xlsx
+++ b/Submission/Table 4.xlsx
@@ -182,7 +182,7 @@
     <t xml:space="preserve">h*</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.3*</t>
+    <t xml:space="preserve">-0.30*</t>
   </si>
   <si>
     <t xml:space="preserve">x</t>
@@ -243,6 +243,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -502,6 +503,9 @@
   </sheetPr>
   <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="10.38"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
